--- a/Result/profitability/6116.xlsx
+++ b/Result/profitability/6116.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.17625</v>
+        <v>-0.10625</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.5175</v>
+        <v>-9.73875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05875</v>
+        <v>0.015</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.32375</v>
+        <v>-3.185</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06375</v>
+        <v>-0.02499999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.855</v>
+        <v>-2.1975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.22</v>
+        <v>-0.17375</v>
       </c>
       <c r="N5" t="n">
-        <v>-16.225</v>
+        <v>-15.04</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2975</v>
+        <v>-0.305</v>
       </c>
       <c r="N6" t="n">
-        <v>-22.53375</v>
+        <v>-21.1425</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.37625</v>
+        <v>-0.33375</v>
       </c>
       <c r="N7" t="n">
-        <v>-21.58125</v>
+        <v>-19.84375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3287499999999999</v>
+        <v>-0.315</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.9925</v>
+        <v>-18.575</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-1.21</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4725</v>
+        <v>-0.4724999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>-19.21375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3070</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3240</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-170</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-5.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-597</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-19.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>727</v>
+      </c>
+      <c r="J75" t="n">
+        <v>130</v>
+      </c>
+      <c r="K75" t="n">
+        <v>137</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-16.85625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>5.235955056179775</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.15625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6307385229540918</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
